--- a/output/yearly_benthic_cover_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_40_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.53254575713407</v>
+        <v>45.62550231662834</v>
       </c>
       <c r="M2" t="n">
-        <v>99.7677842944982</v>
+        <v>98.5136787113918</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03147601884767</v>
+        <v>87.98677704587331</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93495780476427</v>
+        <v>45.88940075702563</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228736546093637</v>
+        <v>2.228656403623713</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710138611509916</v>
+        <v>5.68177306454285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429121820312123</v>
+        <v>0.7428854678745709</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97526232817659</v>
+        <v>33.9598962537922</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17396037343577</v>
+        <v>34.17273152223026</v>
       </c>
       <c r="I3" t="n">
-        <v>6.55726483990547</v>
+        <v>6.557800159593647</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643201137695077</v>
+        <v>4.643034174216068</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96852398115233</v>
+        <v>12.01322295412668</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86114665879039</v>
+        <v>48.86197705372356</v>
       </c>
       <c r="M3" t="n">
-        <v>106.764628444707</v>
+        <v>106.7646007648759</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.11348555982622</v>
+        <v>87.09888660963782</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64979043655453</v>
+        <v>42.63612633131919</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184491017251204</v>
+        <v>2.18596793439796</v>
       </c>
       <c r="E4" t="n">
-        <v>6.509418744616908</v>
+        <v>6.485656838295025</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444687974681761</v>
+        <v>0.7444424161463837</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3007754975526</v>
+        <v>33.3094164473121</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2455646835361</v>
+        <v>34.24435114273365</v>
       </c>
       <c r="I4" t="n">
-        <v>5.475836835225119</v>
+        <v>5.476286729837806</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652929984176101</v>
+        <v>4.652765100914898</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8865144401738</v>
+        <v>12.90111339036216</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28154887771874</v>
+        <v>44.28059916277437</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81785375444706</v>
+        <v>99.81783888445572</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.048286806805</v>
+        <v>85.94562542590501</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43448819764895</v>
+        <v>42.33281783156279</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132851434583616</v>
+        <v>2.129686638605746</v>
       </c>
       <c r="E5" t="n">
-        <v>7.117421064235496</v>
+        <v>7.080617044887529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745787116879738</v>
+        <v>0.7457623749307922</v>
       </c>
       <c r="G5" t="n">
-        <v>32.51357237535139</v>
+        <v>32.45181140643418</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30620737646795</v>
+        <v>34.30506924681644</v>
       </c>
       <c r="I5" t="n">
-        <v>4.57127795878844</v>
+        <v>4.571663870912888</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661169480498363</v>
+        <v>4.661014843317451</v>
       </c>
       <c r="K5" t="n">
-        <v>13.95171319319501</v>
+        <v>14.05437457409498</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4616920303998</v>
+        <v>43.46068851851339</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84789342124375</v>
+        <v>99.84788092417115</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74752869225657</v>
+        <v>84.65731370273306</v>
       </c>
       <c r="C6" t="n">
-        <v>41.8437735930002</v>
+        <v>41.75451905709086</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069523426983007</v>
+        <v>2.066931149615377</v>
       </c>
       <c r="E6" t="n">
-        <v>7.541945092220847</v>
+        <v>7.507879671304124</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469062304663914</v>
+        <v>0.7468827404409161</v>
       </c>
       <c r="G6" t="n">
-        <v>31.5481887930152</v>
+        <v>31.49555368451539</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35768660145401</v>
+        <v>34.35660606028213</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815114607702176</v>
+        <v>3.81544326881939</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668163940414947</v>
+        <v>4.668017127755725</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25247130774344</v>
+        <v>15.34268629726694</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77677515595668</v>
+        <v>42.7758039825613</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87302005670031</v>
+        <v>99.8730093369191</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.38519975371268</v>
+        <v>83.0980657491439</v>
       </c>
       <c r="C7" t="n">
-        <v>41.07411163298907</v>
+        <v>40.78792196851157</v>
       </c>
       <c r="D7" t="n">
-        <v>2.003571369712706</v>
+        <v>1.99099887669513</v>
       </c>
       <c r="E7" t="n">
-        <v>7.832147933500859</v>
+        <v>7.762664201469993</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478566918985817</v>
+        <v>0.7478365425262513</v>
       </c>
       <c r="G7" t="n">
-        <v>30.54280372371717</v>
+        <v>30.3385103168193</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40140782733477</v>
+        <v>34.40048095620755</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183307883182453</v>
+        <v>3.183596464636596</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674104324366136</v>
+        <v>4.67397839078907</v>
       </c>
       <c r="K7" t="n">
-        <v>16.61480024628734</v>
+        <v>16.9019342508561</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20511271495411</v>
+        <v>42.20415924538735</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8940245942305</v>
+        <v>99.89401546475503</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.30932613614829</v>
+        <v>88.03271364022628</v>
       </c>
       <c r="C8" t="n">
-        <v>43.34547185922086</v>
+        <v>43.12463463049117</v>
       </c>
       <c r="D8" t="n">
-        <v>2.00789018597361</v>
+        <v>1.995264010857921</v>
       </c>
       <c r="E8" t="n">
-        <v>9.648874208406552</v>
+        <v>9.619946672609569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494687411076204</v>
+        <v>0.749438564116041</v>
       </c>
       <c r="G8" t="n">
-        <v>31.03267244490321</v>
+        <v>30.85236732976525</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47556209095055</v>
+        <v>34.47417394933788</v>
       </c>
       <c r="I8" t="n">
-        <v>5.710678832884116</v>
+        <v>5.657532087814358</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684179631922628</v>
+        <v>4.683991025725256</v>
       </c>
       <c r="K8" t="n">
-        <v>11.69067386385171</v>
+        <v>11.96728635977372</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77390775675885</v>
+        <v>44.71989773029192</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81005347983142</v>
+        <v>99.81181872055681</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.45205022711195</v>
+        <v>86.09018183574214</v>
       </c>
       <c r="C9" t="n">
-        <v>42.37477950925523</v>
+        <v>42.06025311839443</v>
       </c>
       <c r="D9" t="n">
-        <v>1.924063983825135</v>
+        <v>1.907479607468863</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0406570063551</v>
+        <v>9.983909148841896</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508464614685315</v>
+        <v>0.750809131668856</v>
       </c>
       <c r="G9" t="n">
-        <v>29.73710803020266</v>
+        <v>29.4949747017997</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53893722755247</v>
+        <v>34.53722005676737</v>
       </c>
       <c r="I9" t="n">
-        <v>4.767647133529756</v>
+        <v>4.723232116265105</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692790384178323</v>
+        <v>4.69255707293035</v>
       </c>
       <c r="K9" t="n">
-        <v>13.54794977288804</v>
+        <v>13.90981816425785</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91864075027661</v>
+        <v>43.87277504824177</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84137003241989</v>
+        <v>99.84284633089406</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.35562169592063</v>
+        <v>83.96528734684783</v>
       </c>
       <c r="C10" t="n">
-        <v>41.01842016365034</v>
+        <v>40.66828256147735</v>
       </c>
       <c r="D10" t="n">
-        <v>1.830211059078269</v>
+        <v>1.812376087087748</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21410340731475</v>
+        <v>10.14316041366323</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520271111951636</v>
+        <v>0.7519841528571511</v>
       </c>
       <c r="G10" t="n">
-        <v>28.28657697426575</v>
+        <v>28.02440803534119</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59324711497754</v>
+        <v>34.59127103142895</v>
       </c>
       <c r="I10" t="n">
-        <v>3.979286584119381</v>
+        <v>3.942186671112374</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700169444969773</v>
+        <v>4.699900955357194</v>
       </c>
       <c r="K10" t="n">
-        <v>15.64437830407937</v>
+        <v>16.03471265315219</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20476688967226</v>
+        <v>43.16580389325197</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86756535740196</v>
+        <v>99.8687991078815</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.07562523962596</v>
+        <v>81.75282581716907</v>
       </c>
       <c r="C11" t="n">
-        <v>39.35560078779807</v>
+        <v>39.06699308581398</v>
       </c>
       <c r="D11" t="n">
-        <v>1.729073729199631</v>
+        <v>1.714376841608332</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20309681531716</v>
+        <v>10.14295725232121</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530412731093953</v>
+        <v>0.7529927615635399</v>
       </c>
       <c r="G11" t="n">
-        <v>26.72346279003359</v>
+        <v>26.50906535230912</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6398985630322</v>
+        <v>34.63766703192283</v>
       </c>
       <c r="I11" t="n">
-        <v>3.320544112000257</v>
+        <v>3.289561817671905</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706507956933721</v>
+        <v>4.706204759772124</v>
       </c>
       <c r="K11" t="n">
-        <v>17.92437476037403</v>
+        <v>18.24717418283092</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60948871338014</v>
+        <v>42.57632754604645</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88946426155225</v>
+        <v>99.89049481469135</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.74690472859859</v>
+        <v>79.40866138880156</v>
       </c>
       <c r="C12" t="n">
-        <v>37.54114077885468</v>
+        <v>37.23211136522245</v>
       </c>
       <c r="D12" t="n">
-        <v>1.626791212843781</v>
+        <v>1.611483783603161</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06125830089787</v>
+        <v>9.991609611361344</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539132687317283</v>
+        <v>0.75386023965334</v>
       </c>
       <c r="G12" t="n">
-        <v>25.14264933266194</v>
+        <v>24.91805062744902</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68001036165952</v>
+        <v>34.67757102405364</v>
       </c>
       <c r="I12" t="n">
-        <v>2.770324322230449</v>
+        <v>2.744459604847698</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711957929573302</v>
+        <v>4.711626497833375</v>
       </c>
       <c r="K12" t="n">
-        <v>20.2530952714014</v>
+        <v>20.59133861119844</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11352661329947</v>
+        <v>42.08517330642154</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90776266355554</v>
+        <v>99.90862328284243</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.29317947323112</v>
+        <v>77.11307581946161</v>
       </c>
       <c r="C13" t="n">
-        <v>35.51565412674429</v>
+        <v>35.36059363784467</v>
       </c>
       <c r="D13" t="n">
-        <v>1.519924795344223</v>
+        <v>1.511686278250729</v>
       </c>
       <c r="E13" t="n">
-        <v>9.785469489276768</v>
+        <v>9.754391830363502</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546646163769051</v>
+        <v>0.7546062532031653</v>
       </c>
       <c r="G13" t="n">
-        <v>23.49099001743103</v>
+        <v>23.37490181256936</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71457235333765</v>
+        <v>34.71188764734561</v>
       </c>
       <c r="I13" t="n">
-        <v>2.31090434910888</v>
+        <v>2.289312915209474</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716653852355657</v>
+        <v>4.716289082519784</v>
       </c>
       <c r="K13" t="n">
-        <v>22.70682052676889</v>
+        <v>22.88692418053837</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70057189309153</v>
+        <v>41.67624719259344</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9230465466047</v>
+        <v>99.92376501097648</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.83873436456915</v>
+        <v>83.88070407892572</v>
       </c>
       <c r="C14" t="n">
-        <v>39.47581133007467</v>
+        <v>39.54675024614099</v>
       </c>
       <c r="D14" t="n">
-        <v>1.521815958175391</v>
+        <v>1.51347806191433</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02325829781056</v>
+        <v>12.09255278077794</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556036060406442</v>
+        <v>0.7555006789688768</v>
       </c>
       <c r="G14" t="n">
-        <v>25.224251152914</v>
+        <v>25.23209301450879</v>
       </c>
       <c r="H14" t="n">
-        <v>36.46179840459226</v>
+        <v>36.58251644298783</v>
       </c>
       <c r="I14" t="n">
-        <v>3.129484407282273</v>
+        <v>2.982683856212457</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722522537754027</v>
+        <v>4.721879243555481</v>
       </c>
       <c r="K14" t="n">
-        <v>16.16126563543085</v>
+        <v>16.11929592107429</v>
       </c>
       <c r="L14" t="n">
-        <v>44.25873652140752</v>
+        <v>44.23464874271305</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89581348691304</v>
+        <v>99.90069490992833</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.09201706071903</v>
+        <v>83.25167868986068</v>
       </c>
       <c r="C15" t="n">
-        <v>39.212862323213</v>
+        <v>39.37505815769332</v>
       </c>
       <c r="D15" t="n">
-        <v>1.494068074581173</v>
+        <v>1.490003952243302</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23913920031312</v>
+        <v>12.32347752451028</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563949396371785</v>
+        <v>0.7562533046077021</v>
       </c>
       <c r="G15" t="n">
-        <v>24.76432721731436</v>
+        <v>24.84454859362787</v>
       </c>
       <c r="H15" t="n">
-        <v>36.49998436061066</v>
+        <v>36.62276616979413</v>
       </c>
       <c r="I15" t="n">
-        <v>2.610634895530172</v>
+        <v>2.488045991279245</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727468372732366</v>
+        <v>4.726583153798138</v>
       </c>
       <c r="K15" t="n">
-        <v>16.90798293928097</v>
+        <v>16.74832131013931</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79222461508151</v>
+        <v>43.79376820282815</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91306987757548</v>
+        <v>99.91714767066077</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.63529160561181</v>
+        <v>80.9397413861758</v>
       </c>
       <c r="C16" t="n">
-        <v>37.15979215667336</v>
+        <v>37.4479080145375</v>
       </c>
       <c r="D16" t="n">
-        <v>1.399982959967173</v>
+        <v>1.402091714747262</v>
       </c>
       <c r="E16" t="n">
-        <v>11.83132528088291</v>
+        <v>11.94223303531165</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570757996695759</v>
+        <v>0.7568996019464426</v>
       </c>
       <c r="G16" t="n">
-        <v>23.20485706717895</v>
+        <v>23.3786868063779</v>
       </c>
       <c r="H16" t="n">
-        <v>36.53283939338784</v>
+        <v>36.65406414385738</v>
       </c>
       <c r="I16" t="n">
-        <v>2.177487356590518</v>
+        <v>2.075143571769903</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73172374793485</v>
+        <v>4.730622512165266</v>
       </c>
       <c r="K16" t="n">
-        <v>19.36470839438819</v>
+        <v>19.06025861382421</v>
       </c>
       <c r="L16" t="n">
-        <v>43.4029818129515</v>
+        <v>43.42272098299164</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92748236401304</v>
+        <v>99.93088761135334</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.27900233440111</v>
+        <v>82.70422671754153</v>
       </c>
       <c r="C17" t="n">
-        <v>38.34446715570121</v>
+        <v>38.73730005929136</v>
       </c>
       <c r="D17" t="n">
-        <v>1.401234451915283</v>
+        <v>1.403254735578217</v>
       </c>
       <c r="E17" t="n">
-        <v>12.60190921774147</v>
+        <v>12.75286073167862</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577525752407712</v>
+        <v>0.757527442475522</v>
       </c>
       <c r="G17" t="n">
-        <v>23.61784832222379</v>
+        <v>23.8557893463547</v>
       </c>
       <c r="H17" t="n">
-        <v>36.95774498099441</v>
+        <v>37.14217847444663</v>
       </c>
       <c r="I17" t="n">
-        <v>2.206559191030555</v>
+        <v>2.058069471535824</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735953595254821</v>
+        <v>4.734546515472013</v>
       </c>
       <c r="K17" t="n">
-        <v>17.72099766559888</v>
+        <v>17.29577328245846</v>
       </c>
       <c r="L17" t="n">
-        <v>43.86104889752882</v>
+        <v>43.89838120029322</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92651371882893</v>
+        <v>99.93145454204304</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.94449465099559</v>
+        <v>80.42508960465553</v>
       </c>
       <c r="C18" t="n">
-        <v>36.35070343802558</v>
+        <v>36.77613812535881</v>
       </c>
       <c r="D18" t="n">
-        <v>1.315291625458485</v>
+        <v>1.320056010677581</v>
       </c>
       <c r="E18" t="n">
-        <v>12.13568980332654</v>
+        <v>12.28279218867952</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583339886464876</v>
+        <v>0.7580662990255164</v>
       </c>
       <c r="G18" t="n">
-        <v>22.1692794286561</v>
+        <v>22.44138381841109</v>
       </c>
       <c r="H18" t="n">
-        <v>36.9861021639049</v>
+        <v>37.16859904356372</v>
       </c>
       <c r="I18" t="n">
-        <v>1.840210211962531</v>
+        <v>1.716277875388626</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739587429040548</v>
+        <v>4.737914368909478</v>
       </c>
       <c r="K18" t="n">
-        <v>20.05550534900442</v>
+        <v>19.57491039534447</v>
       </c>
       <c r="L18" t="n">
-        <v>43.53249790210803</v>
+        <v>43.59178288286516</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93870668913803</v>
+        <v>99.94283140356843</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.9713765090691</v>
+        <v>79.59276390099507</v>
       </c>
       <c r="C19" t="n">
-        <v>35.66106145582259</v>
+        <v>36.20834454027057</v>
       </c>
       <c r="D19" t="n">
-        <v>1.280187515015389</v>
+        <v>1.290346449639525</v>
       </c>
       <c r="E19" t="n">
-        <v>12.06754797654674</v>
+        <v>12.24486692004248</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588251644364516</v>
+        <v>0.7585206368751485</v>
       </c>
       <c r="G19" t="n">
-        <v>21.57759860408145</v>
+        <v>21.93631156621983</v>
       </c>
       <c r="H19" t="n">
-        <v>37.0100582020359</v>
+        <v>37.19087559296976</v>
       </c>
       <c r="I19" t="n">
-        <v>1.534501769225353</v>
+        <v>1.431088754778655</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742657277727823</v>
+        <v>4.740753980469679</v>
       </c>
       <c r="K19" t="n">
-        <v>21.0286234909309</v>
+        <v>20.40723609900492</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25919810291423</v>
+        <v>43.33674497529706</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94888304966771</v>
+        <v>99.95232561457256</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.42260238921172</v>
+        <v>77.18422262321228</v>
       </c>
       <c r="C20" t="n">
-        <v>33.34851038594837</v>
+        <v>34.02026662204678</v>
       </c>
       <c r="D20" t="n">
-        <v>1.187424535254265</v>
+        <v>1.20335079198748</v>
       </c>
       <c r="E20" t="n">
-        <v>11.40637204937964</v>
+        <v>11.61817799640387</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592486387690333</v>
+        <v>0.758911501772125</v>
       </c>
       <c r="G20" t="n">
-        <v>20.0140758239206</v>
+        <v>20.45735693996686</v>
       </c>
       <c r="H20" t="n">
-        <v>37.0307122478299</v>
+        <v>37.21004001256551</v>
       </c>
       <c r="I20" t="n">
-        <v>1.27946510175181</v>
+        <v>1.193188494440654</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745303992306459</v>
+        <v>4.743196886075782</v>
       </c>
       <c r="K20" t="n">
-        <v>23.57739761078829</v>
+        <v>22.8157773767877</v>
       </c>
       <c r="L20" t="n">
-        <v>43.03146695411818</v>
+        <v>43.12420353575499</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95737495085484</v>
+        <v>99.96024753458948</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.11129037408463</v>
+        <v>82.90849896236418</v>
       </c>
       <c r="C21" t="n">
-        <v>36.81538720151309</v>
+        <v>37.52599834057856</v>
       </c>
       <c r="D21" t="n">
-        <v>1.18833641690513</v>
+        <v>1.20420960800131</v>
       </c>
       <c r="E21" t="n">
-        <v>13.29823192369889</v>
+        <v>13.5197418670153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598317031083511</v>
+        <v>0.7594531271694257</v>
       </c>
       <c r="G21" t="n">
-        <v>21.59725950274715</v>
+        <v>22.06937556171825</v>
       </c>
       <c r="H21" t="n">
-        <v>38.62696383796678</v>
+        <v>38.8340148091856</v>
       </c>
       <c r="I21" t="n">
-        <v>1.891718845231139</v>
+        <v>1.775121944465375</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748948144427196</v>
+        <v>4.746582044808911</v>
       </c>
       <c r="K21" t="n">
-        <v>17.88870962591536</v>
+        <v>17.09150103763583</v>
       </c>
       <c r="L21" t="n">
-        <v>45.23289426536662</v>
+        <v>45.32337208957788</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93699109279508</v>
+        <v>99.94087146779226</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_40_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.62550231662834</v>
+        <v>45.78034139809846</v>
       </c>
       <c r="M2" t="n">
-        <v>98.5136787113918</v>
+        <v>99.29259498031317</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98677704587331</v>
+        <v>88.05825809621952</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88940075702563</v>
+        <v>45.93394755910583</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228656403623713</v>
+        <v>2.228805991087964</v>
       </c>
       <c r="E3" t="n">
-        <v>5.68177306454285</v>
+        <v>5.71107870479368</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428854678745709</v>
+        <v>0.7429353303626547</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9598962537922</v>
+        <v>33.97462060461213</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17273152223026</v>
+        <v>34.17502519668211</v>
       </c>
       <c r="I3" t="n">
-        <v>6.557800159593647</v>
+        <v>6.582446453914403</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643034174216068</v>
+        <v>4.643345814766591</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01322295412668</v>
+        <v>11.94174190378047</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86197705372356</v>
+        <v>48.88804245527132</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646007648759</v>
+        <v>106.7637319181576</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09888660963782</v>
+        <v>87.20516137339605</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63612633131919</v>
+        <v>42.7185725821877</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18596793439796</v>
+        <v>2.188030238718147</v>
       </c>
       <c r="E4" t="n">
-        <v>6.485656838295025</v>
+        <v>6.522744761870831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444424161463837</v>
+        <v>0.7444963386559326</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3094164473121</v>
+        <v>33.35305878085022</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24435114273365</v>
+        <v>34.24683157817289</v>
       </c>
       <c r="I4" t="n">
-        <v>5.476286729837806</v>
+        <v>5.496897558528444</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652765100914898</v>
+        <v>4.653102116599578</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90111339036216</v>
+        <v>12.79483862660397</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28059916277437</v>
+        <v>44.30374305637736</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81783888445572</v>
+        <v>99.81715426516904</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94562542590501</v>
+        <v>86.06121911411923</v>
       </c>
       <c r="C5" t="n">
-        <v>42.33281783156279</v>
+        <v>42.42784585505838</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129686638605746</v>
+        <v>2.13230909551827</v>
       </c>
       <c r="E5" t="n">
-        <v>7.080617044887529</v>
+        <v>7.12144920756973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457623749307922</v>
+        <v>0.7458195872271021</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45181140643418</v>
+        <v>32.50367812257812</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30506924681644</v>
+        <v>34.30770101244669</v>
       </c>
       <c r="I5" t="n">
-        <v>4.571663870912888</v>
+        <v>4.588889668609925</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661014843317451</v>
+        <v>4.661372420169387</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05437457409498</v>
+        <v>13.9387808858808</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46068851851339</v>
+        <v>43.48068166021283</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84788092417115</v>
+        <v>99.84730840115199</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.65731370273306</v>
+        <v>84.70975704383328</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75451905709086</v>
+        <v>41.78913972991422</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066931149615377</v>
+        <v>2.066407276907436</v>
       </c>
       <c r="E6" t="n">
-        <v>7.507879671304124</v>
+        <v>7.539657743242123</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468827404409161</v>
+        <v>0.7469435695262064</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49555368451539</v>
+        <v>31.49910917695891</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35660606028213</v>
+        <v>34.35940419820549</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81544326881939</v>
+        <v>3.829837769454325</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668017127755725</v>
+        <v>4.66839730953879</v>
       </c>
       <c r="K6" t="n">
-        <v>15.34268629726694</v>
+        <v>15.29024295616673</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7758039825613</v>
+        <v>42.79314815645768</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8730093369191</v>
+        <v>99.87253084253862</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.0980657491439</v>
+        <v>83.26081047467805</v>
       </c>
       <c r="C7" t="n">
-        <v>40.78792196851157</v>
+        <v>40.93509310990369</v>
       </c>
       <c r="D7" t="n">
-        <v>1.99099887669513</v>
+        <v>1.996117452691337</v>
       </c>
       <c r="E7" t="n">
-        <v>7.762664201469993</v>
+        <v>7.815795138506847</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478365425262513</v>
+        <v>0.7478991786757057</v>
       </c>
       <c r="G7" t="n">
-        <v>30.3385103168193</v>
+        <v>30.42765202920548</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40048095620755</v>
+        <v>34.40336221908245</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183596464636596</v>
+        <v>3.195614589793087</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67397839078907</v>
+        <v>4.67436986672316</v>
       </c>
       <c r="K7" t="n">
-        <v>16.9019342508561</v>
+        <v>16.73918952532193</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20415924538735</v>
+        <v>42.21933298228955</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89401546475503</v>
+        <v>99.89361561751517</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.03271364022628</v>
+        <v>88.12773478367899</v>
       </c>
       <c r="C8" t="n">
-        <v>43.12463463049117</v>
+        <v>43.22966988180606</v>
       </c>
       <c r="D8" t="n">
-        <v>1.995264010857921</v>
+        <v>2.000379181831383</v>
       </c>
       <c r="E8" t="n">
-        <v>9.619946672609569</v>
+        <v>9.644066617274396</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749438564116041</v>
+        <v>0.7494959503081974</v>
       </c>
       <c r="G8" t="n">
-        <v>30.85236732976525</v>
+        <v>30.92802387561175</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47417394933788</v>
+        <v>34.47681371417707</v>
       </c>
       <c r="I8" t="n">
-        <v>5.657532087814358</v>
+        <v>5.644605755049961</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683991025725256</v>
+        <v>4.684349689426234</v>
       </c>
       <c r="K8" t="n">
-        <v>11.96728635977372</v>
+        <v>11.872265216321</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71989773029192</v>
+        <v>44.71031223038689</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81181872055681</v>
+        <v>99.81224732851396</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.09018183574214</v>
+        <v>86.1441154954333</v>
       </c>
       <c r="C9" t="n">
-        <v>42.06025311839443</v>
+        <v>42.12231935831473</v>
       </c>
       <c r="D9" t="n">
-        <v>1.907479607468863</v>
+        <v>1.910651283761145</v>
       </c>
       <c r="E9" t="n">
-        <v>9.983909148841896</v>
+        <v>9.99688028546826</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750809131668856</v>
+        <v>0.750862627624578</v>
       </c>
       <c r="G9" t="n">
-        <v>29.4949747017997</v>
+        <v>29.54073360633183</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53722005676737</v>
+        <v>34.53968087073058</v>
       </c>
       <c r="I9" t="n">
-        <v>4.723232116265105</v>
+        <v>4.712415398863288</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69255707293035</v>
+        <v>4.692891422653612</v>
       </c>
       <c r="K9" t="n">
-        <v>13.90981816425785</v>
+        <v>13.85588450456671</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87277504824177</v>
+        <v>43.8650015328116</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84284633089406</v>
+        <v>99.84320539569305</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.96528734684783</v>
+        <v>83.95810712700961</v>
       </c>
       <c r="C10" t="n">
-        <v>40.66828256147735</v>
+        <v>40.66762157349314</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812376087087748</v>
+        <v>1.812708519589501</v>
       </c>
       <c r="E10" t="n">
-        <v>10.14316041366323</v>
+        <v>10.13994983683937</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519841528571511</v>
+        <v>0.7520351376365998</v>
       </c>
       <c r="G10" t="n">
-        <v>28.02440803534119</v>
+        <v>28.02643262966862</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59127103142895</v>
+        <v>34.59361633128358</v>
       </c>
       <c r="I10" t="n">
-        <v>3.942186671112374</v>
+        <v>3.933145061763206</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699900955357194</v>
+        <v>4.700219610228748</v>
       </c>
       <c r="K10" t="n">
-        <v>16.03471265315219</v>
+        <v>16.04189287299039</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16580389325197</v>
+        <v>43.15958512577026</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8687991078815</v>
+        <v>99.86909957225379</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.75282581716907</v>
+        <v>81.62136221036403</v>
       </c>
       <c r="C11" t="n">
-        <v>39.06699308581398</v>
+        <v>38.94065135455561</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714376841608332</v>
+        <v>1.709044837526255</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14295725232121</v>
+        <v>10.10707707156306</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529927615635399</v>
+        <v>0.7530431212471466</v>
       </c>
       <c r="G11" t="n">
-        <v>26.50906535230912</v>
+        <v>26.42368008004918</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63766703192283</v>
+        <v>34.63998357736873</v>
       </c>
       <c r="I11" t="n">
-        <v>3.289561817671905</v>
+        <v>3.282014014814987</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706204759772124</v>
+        <v>4.706519507794666</v>
       </c>
       <c r="K11" t="n">
-        <v>18.24717418283092</v>
+        <v>18.37863778963598</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57632754604645</v>
+        <v>42.571456826315</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89049481469135</v>
+        <v>99.89074597050659</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.40866138880156</v>
+        <v>79.13823407173881</v>
       </c>
       <c r="C12" t="n">
-        <v>37.23211136522245</v>
+        <v>36.96555225159584</v>
       </c>
       <c r="D12" t="n">
-        <v>1.611483783603161</v>
+        <v>1.59990991471748</v>
       </c>
       <c r="E12" t="n">
-        <v>9.991609611361344</v>
+        <v>9.918027816377467</v>
       </c>
       <c r="F12" t="n">
-        <v>0.75386023965334</v>
+        <v>0.7539116256328522</v>
       </c>
       <c r="G12" t="n">
-        <v>24.91805062744902</v>
+        <v>24.73633623596725</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67757102405364</v>
+        <v>34.67993477911119</v>
       </c>
       <c r="I12" t="n">
-        <v>2.744459604847698</v>
+        <v>2.738166039727245</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711626497833375</v>
+        <v>4.711947660205326</v>
       </c>
       <c r="K12" t="n">
-        <v>20.59133861119844</v>
+        <v>20.8617659282612</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08517330642154</v>
+        <v>42.08151476417589</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90862328284243</v>
+        <v>99.90883294403292</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.11307581946161</v>
+        <v>76.67996000763756</v>
       </c>
       <c r="C13" t="n">
-        <v>35.36059363784467</v>
+        <v>34.9302123674448</v>
       </c>
       <c r="D13" t="n">
-        <v>1.511686278250729</v>
+        <v>1.492906522853945</v>
       </c>
       <c r="E13" t="n">
-        <v>9.754391830363502</v>
+        <v>9.635379773639627</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546062532031653</v>
+        <v>0.7546601860174985</v>
       </c>
       <c r="G13" t="n">
-        <v>23.37490181256936</v>
+        <v>23.08194816375335</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71188764734561</v>
+        <v>34.71436855680492</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289312915209474</v>
+        <v>2.284070641958847</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716289082519784</v>
+        <v>4.716626162609366</v>
       </c>
       <c r="K13" t="n">
-        <v>22.88692418053837</v>
+        <v>23.32003999236245</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67624719259344</v>
+        <v>41.67368747242256</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92376501097648</v>
+        <v>99.92393983222981</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.88070407892572</v>
+        <v>83.52118806963053</v>
       </c>
       <c r="C14" t="n">
-        <v>39.54675024614099</v>
+        <v>39.1855744971442</v>
       </c>
       <c r="D14" t="n">
-        <v>1.51347806191433</v>
+        <v>1.49466109391537</v>
       </c>
       <c r="E14" t="n">
-        <v>12.09255278077794</v>
+        <v>12.00492437329234</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555006789688768</v>
+        <v>0.7555471169159343</v>
       </c>
       <c r="G14" t="n">
-        <v>25.23209301450879</v>
+        <v>24.97649561697687</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58251644298783</v>
+        <v>36.62258726665672</v>
       </c>
       <c r="I14" t="n">
-        <v>2.982683856212457</v>
+        <v>2.944803121148689</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721879243555481</v>
+        <v>4.722169480724589</v>
       </c>
       <c r="K14" t="n">
-        <v>16.11929592107429</v>
+        <v>16.47881193036948</v>
       </c>
       <c r="L14" t="n">
-        <v>44.23464874271305</v>
+        <v>44.23756869783258</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90069490992833</v>
+        <v>99.90195512534625</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.25167868986068</v>
+        <v>82.7156837132501</v>
       </c>
       <c r="C15" t="n">
-        <v>39.37505815769332</v>
+        <v>38.83512427821297</v>
       </c>
       <c r="D15" t="n">
-        <v>1.490003952243302</v>
+        <v>1.464818673016334</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32347752451028</v>
+        <v>12.17463921972199</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562533046077021</v>
+        <v>0.7562950403700455</v>
       </c>
       <c r="G15" t="n">
-        <v>24.84454859362787</v>
+        <v>24.47781461308974</v>
       </c>
       <c r="H15" t="n">
-        <v>36.62276616979413</v>
+        <v>36.65884032269216</v>
       </c>
       <c r="I15" t="n">
-        <v>2.488045991279245</v>
+        <v>2.456431842047059</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726583153798138</v>
+        <v>4.726844002312784</v>
       </c>
       <c r="K15" t="n">
-        <v>16.74832131013931</v>
+        <v>17.2843162867499</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79376820282815</v>
+        <v>43.79875934833855</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91714767066077</v>
+        <v>99.91819991330142</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.9397413861758</v>
+        <v>80.20311644872534</v>
       </c>
       <c r="C16" t="n">
-        <v>37.4479080145375</v>
+        <v>36.70217137084654</v>
       </c>
       <c r="D16" t="n">
-        <v>1.402091714747262</v>
+        <v>1.369427630663273</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94223303531165</v>
+        <v>11.72327126605108</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568996019464426</v>
+        <v>0.7569390196097375</v>
       </c>
       <c r="G16" t="n">
-        <v>23.3786868063779</v>
+        <v>22.88378506289327</v>
       </c>
       <c r="H16" t="n">
-        <v>36.65406414385738</v>
+        <v>36.69005503501851</v>
       </c>
       <c r="I16" t="n">
-        <v>2.075143571769903</v>
+        <v>2.048769561928588</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730622512165266</v>
+        <v>4.730868872560858</v>
       </c>
       <c r="K16" t="n">
-        <v>19.06025861382421</v>
+        <v>19.79688355127468</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42272098299164</v>
+        <v>43.43271086004415</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93088761135334</v>
+        <v>99.93176578216537</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.70422671754153</v>
+        <v>81.88100181509944</v>
       </c>
       <c r="C17" t="n">
-        <v>38.73730005929136</v>
+        <v>37.93064869740827</v>
       </c>
       <c r="D17" t="n">
-        <v>1.403254735578217</v>
+        <v>1.370561626678544</v>
       </c>
       <c r="E17" t="n">
-        <v>12.75286073167862</v>
+        <v>12.50159774158739</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757527442475522</v>
+        <v>0.7575658258847251</v>
       </c>
       <c r="G17" t="n">
-        <v>23.8557893463547</v>
+        <v>23.33233312543582</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14217847444663</v>
+        <v>37.1500357974596</v>
       </c>
       <c r="I17" t="n">
-        <v>2.058069471535824</v>
+        <v>2.034121286273842</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734546515472013</v>
+        <v>4.734786411779531</v>
       </c>
       <c r="K17" t="n">
-        <v>17.29577328245846</v>
+        <v>18.11899818490054</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89838120029322</v>
+        <v>43.88260517555027</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93145454204304</v>
+        <v>99.93225205785907</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.42508960465553</v>
+        <v>79.44176128660489</v>
       </c>
       <c r="C18" t="n">
-        <v>36.77613812535881</v>
+        <v>35.80533463640771</v>
       </c>
       <c r="D18" t="n">
-        <v>1.320056010677581</v>
+        <v>1.281614962168764</v>
       </c>
       <c r="E18" t="n">
-        <v>12.28279218867952</v>
+        <v>11.97298738206382</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580662990255164</v>
+        <v>0.7581050320619485</v>
       </c>
       <c r="G18" t="n">
-        <v>22.44138381841109</v>
+        <v>21.81811211826522</v>
       </c>
       <c r="H18" t="n">
-        <v>37.16859904356372</v>
+        <v>37.17647776210692</v>
       </c>
       <c r="I18" t="n">
-        <v>1.716277875388626</v>
+        <v>1.69630757955104</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737914368909478</v>
+        <v>4.738156450387177</v>
       </c>
       <c r="K18" t="n">
-        <v>19.57491039534447</v>
+        <v>20.55823871339512</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59178288286516</v>
+        <v>43.579923281134</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94283140356843</v>
+        <v>99.94349663093683</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.59276390099507</v>
+        <v>78.44101676428089</v>
       </c>
       <c r="C19" t="n">
-        <v>36.20834454027057</v>
+        <v>35.0656732471734</v>
       </c>
       <c r="D19" t="n">
-        <v>1.290346449639525</v>
+        <v>1.24579445396963</v>
       </c>
       <c r="E19" t="n">
-        <v>12.24486692004248</v>
+        <v>11.87408815449878</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585206368751485</v>
+        <v>0.7585607007921975</v>
       </c>
       <c r="G19" t="n">
-        <v>21.93631156621983</v>
+        <v>21.20830660951911</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19087559296976</v>
+        <v>37.19882315977684</v>
       </c>
       <c r="I19" t="n">
-        <v>1.431088754778655</v>
+        <v>1.414439305773097</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740753980469679</v>
+        <v>4.741004379951233</v>
       </c>
       <c r="K19" t="n">
-        <v>20.40723609900492</v>
+        <v>21.55898323571911</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33674497529706</v>
+        <v>43.32822386211997</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95232561457256</v>
+        <v>99.95288034501247</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.18422262321228</v>
+        <v>75.75819481288563</v>
       </c>
       <c r="C20" t="n">
-        <v>34.02026662204678</v>
+        <v>32.60037787096405</v>
       </c>
       <c r="D20" t="n">
-        <v>1.20335079198748</v>
+        <v>1.149028846555903</v>
       </c>
       <c r="E20" t="n">
-        <v>11.61817799640387</v>
+        <v>11.14833427294687</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758911501772125</v>
+        <v>0.7589543123396975</v>
       </c>
       <c r="G20" t="n">
-        <v>20.45735693996686</v>
+        <v>19.56097653452368</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21004001256551</v>
+        <v>37.21812535449086</v>
       </c>
       <c r="I20" t="n">
-        <v>1.193188494440654</v>
+        <v>1.179311039905534</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743196886075782</v>
+        <v>4.743464452123108</v>
       </c>
       <c r="K20" t="n">
-        <v>22.8157773767877</v>
+        <v>24.24180518711437</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12420353575499</v>
+        <v>43.11852696120565</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96024753458948</v>
+        <v>99.96071001928406</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.90849896236418</v>
+        <v>81.70650597814662</v>
       </c>
       <c r="C21" t="n">
-        <v>37.52599834057856</v>
+        <v>36.29290424232207</v>
       </c>
       <c r="D21" t="n">
-        <v>1.20420960800131</v>
+        <v>1.14982590425207</v>
       </c>
       <c r="E21" t="n">
-        <v>13.5197418670153</v>
+        <v>13.13684293888413</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594531271694257</v>
+        <v>0.7594807833482389</v>
       </c>
       <c r="G21" t="n">
-        <v>22.06937556171825</v>
+        <v>21.27193025762356</v>
       </c>
       <c r="H21" t="n">
-        <v>38.8340148091856</v>
+        <v>38.94132747883977</v>
       </c>
       <c r="I21" t="n">
-        <v>1.775121944465375</v>
+        <v>1.700343719272375</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746582044808911</v>
+        <v>4.746754895926492</v>
       </c>
       <c r="K21" t="n">
-        <v>17.09150103763583</v>
+        <v>18.29349402185337</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32337208957788</v>
+        <v>45.35696290104448</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94087146779226</v>
+        <v>99.94336116521991</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_40_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.78034139809846</v>
+        <v>43.38418892490697</v>
       </c>
       <c r="M2" t="n">
-        <v>99.29259498031317</v>
+        <v>96.25584588024176</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05825809621952</v>
+        <v>81.50389839064673</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93394755910583</v>
+        <v>43.25945394620228</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228805991087964</v>
+        <v>2.181472438731233</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71107870479368</v>
+        <v>4.155924133419136</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429353303626547</v>
+        <v>0.737652027040593</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97462060461213</v>
+        <v>32.81298126591565</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17502519668211</v>
+        <v>33.93199324386727</v>
       </c>
       <c r="I3" t="n">
-        <v>6.582446453914403</v>
+        <v>3.073550112669137</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643345814766591</v>
+        <v>4.610325169003706</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94174190378047</v>
+        <v>18.49610160935328</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88804245527132</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637319181576</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20516137339605</v>
+        <v>88.58961562043642</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7185725821877</v>
+        <v>42.81993514988918</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188030238718147</v>
+        <v>2.187228553799094</v>
       </c>
       <c r="E4" t="n">
-        <v>6.522744761870831</v>
+        <v>6.516244266552982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444963386559326</v>
+        <v>0.7395984233701088</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35305878085022</v>
+        <v>33.48985019448538</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24683157817289</v>
+        <v>34.021527475025</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496897558528444</v>
+        <v>7.012676561140668</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653102116599578</v>
+        <v>4.62249014606318</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79483862660397</v>
+        <v>11.41038437956357</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30374305637736</v>
+        <v>45.53653975900931</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81715426516904</v>
+        <v>99.76685928846206</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.06121911411923</v>
+        <v>87.55601836758642</v>
       </c>
       <c r="C5" t="n">
-        <v>42.42784585505838</v>
+        <v>42.87330704107153</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13230909551827</v>
+        <v>2.138406241720042</v>
       </c>
       <c r="E5" t="n">
-        <v>7.12144920756973</v>
+        <v>7.346946278450575</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458195872271021</v>
+        <v>0.7412475673945689</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50367812257812</v>
+        <v>32.74230512662501</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30770101244669</v>
+        <v>34.09738810015016</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588889668609925</v>
+        <v>5.856927757030014</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661372420169387</v>
+        <v>4.632797296216055</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9387808858808</v>
+        <v>12.44398163241358</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48068166021283</v>
+        <v>44.48791475537207</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84730840115199</v>
+        <v>99.80520342885718</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.70975704383328</v>
+        <v>86.30135429794736</v>
       </c>
       <c r="C6" t="n">
-        <v>41.78913972991422</v>
+        <v>42.52770333302752</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066407276907436</v>
+        <v>2.078788986539748</v>
       </c>
       <c r="E6" t="n">
-        <v>7.539657743242123</v>
+        <v>7.957117203689728</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469435695262064</v>
+        <v>0.7426475818720488</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49910917695891</v>
+        <v>31.82947279297314</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35940419820549</v>
+        <v>34.16178876611424</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829837769454325</v>
+        <v>4.889991580058138</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66839730953879</v>
+        <v>4.641547386700306</v>
       </c>
       <c r="K6" t="n">
-        <v>15.29024295616673</v>
+        <v>13.69864570205264</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79314815645768</v>
+        <v>43.61095852722456</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87253084253862</v>
+        <v>99.83730756230473</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.26081047467805</v>
+        <v>84.88672142147273</v>
       </c>
       <c r="C7" t="n">
-        <v>40.93509310990369</v>
+        <v>41.87255918583033</v>
       </c>
       <c r="D7" t="n">
-        <v>1.996117452691337</v>
+        <v>2.011765786478641</v>
       </c>
       <c r="E7" t="n">
-        <v>7.815795138506847</v>
+        <v>8.380822115252245</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478991786757057</v>
+        <v>0.7438378481316603</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42765202920548</v>
+        <v>30.80324399502574</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40336221908245</v>
+        <v>34.21654101405637</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195614589793087</v>
+        <v>4.081524111705186</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67436986672316</v>
+        <v>4.648986550822877</v>
       </c>
       <c r="K7" t="n">
-        <v>16.73918952532193</v>
+        <v>15.11327857852728</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21933298228955</v>
+        <v>42.87832913619633</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89361561751517</v>
+        <v>99.86416690055394</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.12773478367899</v>
+        <v>83.31325519775028</v>
       </c>
       <c r="C8" t="n">
-        <v>43.22966988180606</v>
+        <v>40.93308187001378</v>
       </c>
       <c r="D8" t="n">
-        <v>2.000379181831383</v>
+        <v>1.937563517064766</v>
       </c>
       <c r="E8" t="n">
-        <v>9.644066617274396</v>
+        <v>8.639353450458371</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494959503081974</v>
+        <v>0.7448514687608049</v>
       </c>
       <c r="G8" t="n">
-        <v>30.92802387561175</v>
+        <v>29.66709254782322</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47681371417707</v>
+        <v>34.26316756299702</v>
       </c>
       <c r="I8" t="n">
-        <v>5.644605755049961</v>
+        <v>3.405904970891071</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684349689426234</v>
+        <v>4.65532167975503</v>
       </c>
       <c r="K8" t="n">
-        <v>11.872265216321</v>
+        <v>16.68674480224973</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71031223038689</v>
+        <v>42.2667976579669</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81224732851396</v>
+        <v>99.8866243302304</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.1441154954333</v>
+        <v>81.62718259269886</v>
       </c>
       <c r="C9" t="n">
-        <v>42.12231935831473</v>
+        <v>39.77583073612395</v>
       </c>
       <c r="D9" t="n">
-        <v>1.910651283761145</v>
+        <v>1.85854100206933</v>
       </c>
       <c r="E9" t="n">
-        <v>9.99688028546826</v>
+        <v>8.760593201271668</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750862627624578</v>
+        <v>0.7457157767953437</v>
       </c>
       <c r="G9" t="n">
-        <v>29.54073360633183</v>
+        <v>28.45713568959187</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53968087073058</v>
+        <v>34.30292573258581</v>
       </c>
       <c r="I9" t="n">
-        <v>4.712415398863288</v>
+        <v>2.841547585413948</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692891422653612</v>
+        <v>4.660723604970897</v>
       </c>
       <c r="K9" t="n">
-        <v>13.85588450456671</v>
+        <v>18.37281740730114</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8650015328116</v>
+        <v>41.75674338516127</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84320539569305</v>
+        <v>99.90539152858636</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.95810712700961</v>
+        <v>86.29585251875807</v>
       </c>
       <c r="C10" t="n">
-        <v>40.66762157349314</v>
+        <v>43.00497094243224</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812708519589501</v>
+        <v>1.860610645242002</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13994983683937</v>
+        <v>10.60385815700976</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520351376365998</v>
+        <v>0.7465461946147407</v>
       </c>
       <c r="G10" t="n">
-        <v>28.02643262966862</v>
+        <v>29.84184563129388</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59361633128358</v>
+        <v>35.69414545773509</v>
       </c>
       <c r="I10" t="n">
-        <v>3.933145061763206</v>
+        <v>2.882932716520478</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700219610228748</v>
+        <v>4.665913716342128</v>
       </c>
       <c r="K10" t="n">
-        <v>16.04189287299039</v>
+        <v>13.70414748124193</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15958512577026</v>
+        <v>43.19489071308312</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86909957225379</v>
+        <v>99.9040091367573</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.62136221036403</v>
+        <v>86.17905399438382</v>
       </c>
       <c r="C11" t="n">
-        <v>38.94065135455561</v>
+        <v>43.22567265211615</v>
       </c>
       <c r="D11" t="n">
-        <v>1.709044837526255</v>
+        <v>1.84682438660638</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10707707156306</v>
+        <v>10.99320295239186</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530431212471466</v>
+        <v>0.7472551629042643</v>
       </c>
       <c r="G11" t="n">
-        <v>26.42368008004918</v>
+        <v>29.67944002954427</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63998357736873</v>
+        <v>35.78675149525317</v>
       </c>
       <c r="I11" t="n">
-        <v>3.282014014814987</v>
+        <v>2.455235199532225</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706519507794666</v>
+        <v>4.670344768151651</v>
       </c>
       <c r="K11" t="n">
-        <v>18.37863778963598</v>
+        <v>13.82094600561617</v>
       </c>
       <c r="L11" t="n">
-        <v>42.571456826315</v>
+        <v>42.87161781685329</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89074597050659</v>
+        <v>99.91823647458561</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.13823407173881</v>
+        <v>84.43819933025928</v>
       </c>
       <c r="C12" t="n">
-        <v>36.96555225159584</v>
+        <v>41.86687275614617</v>
       </c>
       <c r="D12" t="n">
-        <v>1.59990991471748</v>
+        <v>1.772642488055256</v>
       </c>
       <c r="E12" t="n">
-        <v>9.918027816377467</v>
+        <v>10.89291651493936</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539116256328522</v>
+        <v>0.747859210951497</v>
       </c>
       <c r="G12" t="n">
-        <v>24.73633623596725</v>
+        <v>28.48729787174468</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67993477911119</v>
+        <v>35.81567992349379</v>
       </c>
       <c r="I12" t="n">
-        <v>2.738166039727245</v>
+        <v>2.047683252627852</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711947660205326</v>
+        <v>4.674120068446856</v>
       </c>
       <c r="K12" t="n">
-        <v>20.8617659282612</v>
+        <v>15.5618006697407</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08151476417589</v>
+        <v>42.50312559634834</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90883294403292</v>
+        <v>99.93179902223521</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.67996000763756</v>
+        <v>85.69162607670235</v>
       </c>
       <c r="C13" t="n">
-        <v>34.9302123674448</v>
+        <v>42.90627622147628</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492906522853945</v>
+        <v>1.773944699055151</v>
       </c>
       <c r="E13" t="n">
-        <v>9.635379773639627</v>
+        <v>11.56144407484539</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546601860174985</v>
+        <v>0.7484086000682737</v>
       </c>
       <c r="G13" t="n">
-        <v>23.08194816375335</v>
+        <v>28.8539984715922</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71436855680492</v>
+        <v>36.18776406784254</v>
       </c>
       <c r="I13" t="n">
-        <v>2.284070641958847</v>
+        <v>1.888512412872086</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716626162609366</v>
+        <v>4.677553750426711</v>
       </c>
       <c r="K13" t="n">
-        <v>23.32003999236245</v>
+        <v>14.30837392329767</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67368747242256</v>
+        <v>42.72244565187893</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92393983222981</v>
+        <v>99.93709579665287</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.52118806963053</v>
+        <v>83.99124887042392</v>
       </c>
       <c r="C14" t="n">
-        <v>39.1855744971442</v>
+        <v>41.49971202995926</v>
       </c>
       <c r="D14" t="n">
-        <v>1.49466109391537</v>
+        <v>1.703512603252654</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00492437329234</v>
+        <v>11.36486975369814</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555471169159343</v>
+        <v>0.7488763281088465</v>
       </c>
       <c r="G14" t="n">
-        <v>24.97649561697687</v>
+        <v>27.70838914920537</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62258726665672</v>
+        <v>36.21038009868267</v>
       </c>
       <c r="I14" t="n">
-        <v>2.944803121148689</v>
+        <v>1.57474388679594</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722169480724589</v>
+        <v>4.680477050680291</v>
       </c>
       <c r="K14" t="n">
-        <v>16.47881193036948</v>
+        <v>16.0087511295761</v>
       </c>
       <c r="L14" t="n">
-        <v>44.23756869783258</v>
+        <v>42.43907816232932</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90195512534625</v>
+        <v>99.94754132186469</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.7156837132501</v>
+        <v>83.3202734019564</v>
       </c>
       <c r="C15" t="n">
-        <v>38.83512427821297</v>
+        <v>41.05834723781321</v>
       </c>
       <c r="D15" t="n">
-        <v>1.464818673016334</v>
+        <v>1.675641390568544</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17463921972199</v>
+        <v>11.40018644445162</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562950403700455</v>
+        <v>0.7492740574511452</v>
       </c>
       <c r="G15" t="n">
-        <v>24.47781461308974</v>
+        <v>27.25505149520914</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65884032269216</v>
+        <v>36.22961148592307</v>
       </c>
       <c r="I15" t="n">
-        <v>2.456431842047059</v>
+        <v>1.327545669283229</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726844002312784</v>
+        <v>4.682962859069658</v>
       </c>
       <c r="K15" t="n">
-        <v>17.2843162867499</v>
+        <v>16.67972659804359</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79875934833855</v>
+        <v>42.21769813140837</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91819991330142</v>
+        <v>99.95577196726516</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.20311644872534</v>
+        <v>81.15766974156446</v>
       </c>
       <c r="C16" t="n">
-        <v>36.70217137084654</v>
+        <v>39.10193107024453</v>
       </c>
       <c r="D16" t="n">
-        <v>1.369427630663273</v>
+        <v>1.586511803214851</v>
       </c>
       <c r="E16" t="n">
-        <v>11.72327126605108</v>
+        <v>10.97826057146681</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569390196097375</v>
+        <v>0.7496146659463048</v>
       </c>
       <c r="G16" t="n">
-        <v>22.88378506289327</v>
+        <v>25.80531916778827</v>
       </c>
       <c r="H16" t="n">
-        <v>36.69005503501851</v>
+        <v>36.24608091166352</v>
       </c>
       <c r="I16" t="n">
-        <v>2.048769561928588</v>
+        <v>1.106790959320313</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730868872560858</v>
+        <v>4.685091662164405</v>
       </c>
       <c r="K16" t="n">
-        <v>19.79688355127468</v>
+        <v>18.8423302584355</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43271086004415</v>
+        <v>42.01886240272876</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93176578216537</v>
+        <v>99.96312373140879</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.88100181509944</v>
+        <v>85.4520796368661</v>
       </c>
       <c r="C17" t="n">
-        <v>37.93064869740827</v>
+        <v>41.92795897545511</v>
       </c>
       <c r="D17" t="n">
-        <v>1.370561626678544</v>
+        <v>1.587286629931007</v>
       </c>
       <c r="E17" t="n">
-        <v>12.50159774158739</v>
+        <v>12.49276784815202</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575658258847251</v>
+        <v>0.7499807656304175</v>
       </c>
       <c r="G17" t="n">
-        <v>23.33233312543582</v>
+        <v>27.1184006690719</v>
       </c>
       <c r="H17" t="n">
-        <v>37.1500357974596</v>
+        <v>37.56426151219102</v>
       </c>
       <c r="I17" t="n">
-        <v>2.034121286273842</v>
+        <v>1.252002426699635</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734786411779531</v>
+        <v>4.687379785190109</v>
       </c>
       <c r="K17" t="n">
-        <v>18.11899818490054</v>
+        <v>14.54792036313389</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88260517555027</v>
+        <v>43.48240761916313</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93225205785907</v>
+        <v>99.95828695775214</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.44176128660489</v>
+        <v>87.0172112794075</v>
       </c>
       <c r="C18" t="n">
-        <v>35.80533463640771</v>
+        <v>42.64397657683661</v>
       </c>
       <c r="D18" t="n">
-        <v>1.281614962168764</v>
+        <v>1.588536003644881</v>
       </c>
       <c r="E18" t="n">
-        <v>11.97298738206382</v>
+        <v>13.08081376464688</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581050320619485</v>
+        <v>0.7505710851334112</v>
       </c>
       <c r="G18" t="n">
-        <v>21.81811211826522</v>
+        <v>27.25762134564091</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17647776210692</v>
+        <v>37.59382882538414</v>
       </c>
       <c r="I18" t="n">
-        <v>1.69630757955104</v>
+        <v>2.054770972873468</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738156450387177</v>
+        <v>4.69106928208382</v>
       </c>
       <c r="K18" t="n">
-        <v>20.55823871339512</v>
+        <v>12.9827887205925</v>
       </c>
       <c r="L18" t="n">
-        <v>43.579923281134</v>
+        <v>44.30479620562928</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94349663093683</v>
+        <v>99.93156150305839</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.44101676428089</v>
+        <v>84.58590327236324</v>
       </c>
       <c r="C19" t="n">
-        <v>35.0656732471734</v>
+        <v>40.53161904936535</v>
       </c>
       <c r="D19" t="n">
-        <v>1.24579445396963</v>
+        <v>1.497428641060537</v>
       </c>
       <c r="E19" t="n">
-        <v>11.87408815449878</v>
+        <v>12.61616694175068</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585607007921975</v>
+        <v>0.7510778983270416</v>
       </c>
       <c r="G19" t="n">
-        <v>21.20830660951911</v>
+        <v>25.69431400767313</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19882315977684</v>
+        <v>37.61921356085447</v>
       </c>
       <c r="I19" t="n">
-        <v>1.414439305773097</v>
+        <v>1.713465358153364</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741004379951233</v>
+        <v>4.694236864544011</v>
       </c>
       <c r="K19" t="n">
-        <v>21.55898323571911</v>
+        <v>15.41409672763677</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32822386211997</v>
+        <v>43.99720725152918</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95288034501247</v>
+        <v>99.9429230285313</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.75819481288563</v>
+        <v>82.02333559726115</v>
       </c>
       <c r="C20" t="n">
-        <v>32.60037787096405</v>
+        <v>38.23440111345285</v>
       </c>
       <c r="D20" t="n">
-        <v>1.149028846555903</v>
+        <v>1.40184763398238</v>
       </c>
       <c r="E20" t="n">
-        <v>11.14833427294687</v>
+        <v>12.04899532729588</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589543123396975</v>
+        <v>0.7515139846518433</v>
       </c>
       <c r="G20" t="n">
-        <v>19.56097653452368</v>
+        <v>24.05424359517158</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21812535449086</v>
+        <v>37.64105580201244</v>
       </c>
       <c r="I20" t="n">
-        <v>1.179311039905534</v>
+        <v>1.428716850073023</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743464452123108</v>
+        <v>4.696962404074021</v>
       </c>
       <c r="K20" t="n">
-        <v>24.24180518711437</v>
+        <v>17.97666440273884</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11852696120565</v>
+        <v>43.74133822385961</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96071001928406</v>
+        <v>99.9524037400513</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.70650597814662</v>
+        <v>79.52273583725115</v>
       </c>
       <c r="C21" t="n">
-        <v>36.29290424232207</v>
+        <v>35.95443367693515</v>
       </c>
       <c r="D21" t="n">
-        <v>1.14982590425207</v>
+        <v>1.309034668589013</v>
       </c>
       <c r="E21" t="n">
-        <v>13.13684293888413</v>
+        <v>11.4497922567294</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594807833482389</v>
+        <v>0.7518892221336291</v>
       </c>
       <c r="G21" t="n">
-        <v>21.27193025762356</v>
+        <v>22.46166989155156</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94132747883977</v>
+        <v>37.6598503092064</v>
       </c>
       <c r="I21" t="n">
-        <v>1.700343719272375</v>
+        <v>1.191191850705967</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746754895926492</v>
+        <v>4.699307638335182</v>
       </c>
       <c r="K21" t="n">
-        <v>18.29349402185337</v>
+        <v>20.47726416274885</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35696290104448</v>
+        <v>43.52861558114731</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94336116521991</v>
+        <v>99.96031342083131</v>
       </c>
     </row>
   </sheetData>
